--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MICHIGAN_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MICHIGAN_2011.xlsx
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C131">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C482">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C529">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C535">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C750">
